--- a/ig/nr-add-marital-status-binding/CodeSystem-fr-core-cs-marital-status.xlsx
+++ b/ig/nr-add-marital-status-binding/CodeSystem-fr-core-cs-marital-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:41:10+00:00</t>
+    <t>2024-01-29T10:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-marital-status-binding/CodeSystem-fr-core-cs-marital-status.xlsx
+++ b/ig/nr-add-marital-status-binding/CodeSystem-fr-core-cs-marital-status.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:18:33+00:00</t>
+    <t>2024-01-29T10:24:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -136,9 +136,6 @@
   </si>
   <si>
     <t>Definition</t>
-  </si>
-  <si>
-    <t>P</t>
   </si>
   <si>
     <t>PACS</t>
@@ -484,7 +481,7 @@
         <v>41</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" s="2"/>
     </row>
